--- a/tests/data/xlsx/TestObjectExt.xlsx
+++ b/tests/data/xlsx/TestObjectExt.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20805" windowHeight="9975" tabRatio="500"/>
+    <workbookView windowWidth="20805" windowHeight="9975" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="$Funds$" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>{{Funds.Id}}</t>
   </si>
@@ -42,6 +43,21 @@
   </si>
   <si>
     <t>{{Funds.SetupDate.Year}}</t>
+  </si>
+  <si>
+    <t>{{Id}}</t>
+  </si>
+  <si>
+    <t>{{Name}}</t>
+  </si>
+  <si>
+    <t>{{SetupDate}}</t>
+  </si>
+  <si>
+    <t>{{NetValues.Date}}</t>
+  </si>
+  <si>
+    <t>{{NetValues.Value}}</t>
   </si>
 </sst>
 </file>
@@ -1080,4 +1096,40 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="11.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="26.2857142857143" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>